--- a/data/trans_dic/P56$familiarvive-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 52,84</t>
+          <t>7,4; 52,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 39,1</t>
+          <t>4,83; 40,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 38,01</t>
+          <t>4,68; 41,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 37,72</t>
+          <t>13,83; 40,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 33,93</t>
+          <t>4,07; 33,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 38,29</t>
+          <t>10,95; 37,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 40,93</t>
+          <t>13,74; 42,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 31,48</t>
+          <t>14,28; 31,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 32,07</t>
+          <t>7,56; 33,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 32,75</t>
+          <t>12,03; 33,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 36,47</t>
+          <t>13,22; 35,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,79; 30,13</t>
+          <t>16,55; 30,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 31,42</t>
+          <t>7,82; 33,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 35,94</t>
+          <t>9,94; 35,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 26,13</t>
+          <t>7,77; 25,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,58</t>
+          <t>4,49; 14,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,12; 63,92</t>
+          <t>37,12; 61,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,54; 37,3</t>
+          <t>22,43; 37,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 36,36</t>
+          <t>18,65; 36,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 25,77</t>
+          <t>17,56; 26,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,84; 49,71</t>
+          <t>28,8; 49,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,14; 34,04</t>
+          <t>20,72; 33,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 31,4</t>
+          <t>17,63; 31,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 21,62</t>
+          <t>14,64; 21,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 31,33</t>
+          <t>9,48; 31,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 32,2</t>
+          <t>10,89; 31,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,67</t>
+          <t>9,32; 25,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,7</t>
+          <t>8,63; 19,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,49; 51,48</t>
+          <t>30,27; 51,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,53; 35,76</t>
+          <t>22,16; 35,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 34,73</t>
+          <t>19,62; 34,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 25,77</t>
+          <t>17,97; 25,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,57; 41,94</t>
+          <t>26,23; 41,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,46; 31,17</t>
+          <t>19,94; 31,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,4; 29,99</t>
+          <t>18,57; 29,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 22,21</t>
+          <t>16,14; 22,32</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>20661</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>931; 6798</t>
+          <t>953; 6789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1010; 8379</t>
+          <t>1034; 8615</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>984; 8020</t>
+          <t>987; 8811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3683; 11184</t>
+          <t>4283; 12654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>891; 7488</t>
+          <t>899; 7417</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4759; 16134</t>
+          <t>4612; 16007</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5240; 16856</t>
+          <t>5658; 17325</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7756; 16685</t>
+          <t>8494; 18647</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1950; 11203</t>
+          <t>2643; 11673</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7425; 20817</t>
+          <t>7646; 21168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7884; 22714</t>
+          <t>8235; 22121</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13052; 24899</t>
+          <t>14970; 27702</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>46363</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>52955</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2684; 11128</t>
+          <t>2771; 11851</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5784; 20513</t>
+          <t>5671; 20077</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3973; 13326</t>
+          <t>3962; 13065</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3299; 10557</t>
+          <t>3480; 11356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27243; 45684</t>
+          <t>26533; 44078</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36757; 60839</t>
+          <t>36582; 61965</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25831; 47483</t>
+          <t>24355; 47686</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34565; 51040</t>
+          <t>37927; 56515</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31898; 53133</t>
+          <t>30785; 52414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46553; 74947</t>
+          <t>45613; 73858</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31026; 57023</t>
+          <t>32009; 56486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40787; 58477</t>
+          <t>42980; 63194</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>73617</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4817; 15129</t>
+          <t>4577; 15035</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8874; 25277</t>
+          <t>8549; 24337</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7062; 18504</t>
+          <t>6720; 18714</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8866; 20107</t>
+          <t>9375; 21685</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28525; 48161</t>
+          <t>28318; 48416</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46249; 73395</t>
+          <t>45488; 72089</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33564; 59659</t>
+          <t>33698; 59433</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45255; 64689</t>
+          <t>49485; 70898</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37688; 59486</t>
+          <t>37203; 58298</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58046; 88452</t>
+          <t>56592; 89886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44872; 73135</t>
+          <t>45284; 73120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57999; 78421</t>
+          <t>61989; 85717</t>
         </is>
       </c>
     </row>
